--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122523991</v>
+        <v>122523900</v>
       </c>
       <c r="B2" t="n">
         <v>98211</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,7 +725,7 @@
         <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6568564</v>
+        <v>6568570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523900</v>
+        <v>122524035</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,45 +957,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568570</v>
+        <v>6568578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1042,7 +1039,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1059,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122524035</v>
+        <v>122523991</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,42 +1099,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568578</v>
+        <v>6568564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1174,7 +1184,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,16 +1205,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122523900</v>
+        <v>122524091</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>220787</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -705,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R2" t="n">
         <v>6568570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524091</v>
+        <v>122523991</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,6 +833,11 @@
       <c r="E3" t="n">
         <v>220787</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -840,7 +850,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,17 +863,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568570</v>
+        <v>6568564</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +917,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +937,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524035</v>
+        <v>122523900</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,42 +967,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568578</v>
+        <v>6568570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1039,7 +1057,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,17 +1077,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1087,10 +1095,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122523991</v>
+        <v>122524035</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,45 +1107,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568564</v>
+        <v>6568578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1184,7 +1194,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,6 +1215,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524091</v>
+        <v>122523900</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
         <v>6568570</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -818,7 +818,7 @@
         <v>122523991</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -955,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523900</v>
+        <v>122524035</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,50 +967,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568570</v>
+        <v>6568578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1057,7 +1054,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,7 +1074,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1095,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122524035</v>
+        <v>122524091</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,36 +1119,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1144,13 +1159,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R5" t="n">
-        <v>6568578</v>
+        <v>6568570</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1194,7 +1209,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1214,22 +1229,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -815,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122523991</v>
+        <v>122524035</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,50 +827,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568564</v>
+        <v>6568578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,7 +914,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,6 +935,21 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -955,10 +967,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524035</v>
+        <v>122523991</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,47 +979,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568578</v>
+        <v>6568564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1054,7 +1069,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,21 +1090,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122523900</v>
+        <v>122524091</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R2" t="n">
         <v>6568570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -967,10 +967,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523991</v>
+        <v>122523900</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1022,7 +1022,7 @@
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568564</v>
+        <v>6568570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122524091</v>
+        <v>122523991</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568570</v>
+        <v>6568564</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524091</v>
+        <v>122524035</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6568570</v>
+        <v>6568578</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +794,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -815,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524035</v>
+        <v>122523900</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,47 +839,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568578</v>
+        <v>6568570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,7 +929,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,22 +949,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -967,7 +967,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523900</v>
+        <v>122523991</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1022,7 +1022,7 @@
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568570</v>
+        <v>6568564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122523991</v>
+        <v>122524091</v>
       </c>
       <c r="B5" t="n">
         <v>98240</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R5" t="n">
-        <v>6568564</v>
+        <v>6568570</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -827,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122523900</v>
+        <v>122524091</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -875,17 +875,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R3" t="n">
         <v>6568570</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -967,10 +967,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523991</v>
+        <v>122523900</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1022,7 +1022,7 @@
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568564</v>
+        <v>6568570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122524091</v>
+        <v>122523991</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568570</v>
+        <v>6568564</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524035</v>
+        <v>122524091</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R2" t="n">
-        <v>6568578</v>
+        <v>6568570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +797,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -827,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122524091</v>
+        <v>122523900</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -862,7 +850,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -875,17 +863,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
         <v>6568570</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -929,7 +917,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -967,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523900</v>
+        <v>122523991</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,7 +990,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1022,7 +1010,7 @@
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568570</v>
+        <v>6568564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1069,7 +1057,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,7 +1077,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1095,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122523991</v>
+        <v>122524035</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,50 +1107,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568564</v>
+        <v>6568578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1209,7 +1194,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,6 +1215,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524091</v>
+        <v>122523900</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
         <v>6568570</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -815,7 +815,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122523900</v>
+        <v>122524091</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -850,7 +850,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -863,17 +863,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R3" t="n">
         <v>6568570</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -955,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523991</v>
+        <v>122524035</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,50 +967,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568564</v>
+        <v>6568578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1057,7 +1054,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,6 +1075,21 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1095,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122524035</v>
+        <v>122523991</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,47 +1119,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568578</v>
+        <v>6568564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1194,7 +1209,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,21 +1230,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524035</v>
+        <v>122524091</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R2" t="n">
-        <v>6568578</v>
+        <v>6568570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +797,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -830,7 +818,7 @@
         <v>122523900</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -967,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524091</v>
+        <v>122523991</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,7 +990,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1015,17 +1003,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568570</v>
+        <v>6568564</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1069,7 +1057,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,7 +1077,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1095,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122523991</v>
+        <v>122524035</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,50 +1107,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568564</v>
+        <v>6568578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1209,7 +1194,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,6 +1215,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122523900</v>
+        <v>122523991</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -850,7 +850,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -870,7 +870,7 @@
         <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568570</v>
+        <v>6568564</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -955,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122523991</v>
+        <v>122524035</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,50 +967,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568564</v>
+        <v>6568578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1057,7 +1054,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,6 +1075,21 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1095,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122524035</v>
+        <v>122523900</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,47 +1119,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6568578</v>
+        <v>6568570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1194,7 +1209,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1214,22 +1229,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122524091</v>
+        <v>122524035</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572670</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6568570</v>
+        <v>6568578</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
+          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +794,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -815,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122523991</v>
+        <v>122523900</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -850,7 +862,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -870,7 +882,7 @@
         <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6568564</v>
+        <v>6568570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,7 +929,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
+          <t>Växer i en sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +949,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -955,10 +967,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122524035</v>
+        <v>122523991</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,47 +979,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>572671</v>
       </c>
       <c r="R4" t="n">
-        <v>6568578</v>
+        <v>6568564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1054,7 +1069,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och äldre gnagspår på granlåga. Under växer knärot. Fuktig sänka mellan hällmarker.</t>
+          <t>Två knärot. Äldre skogsparti. Fuktig sänka mellan hällmarker.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,21 +1090,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122523900</v>
+        <v>122524091</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Näshulta kvarn, Srm</t>
+          <t>Söder om Kvarnstallet, Näshulta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572671</v>
+        <v>572670</v>
       </c>
       <c r="R5" t="n">
         <v>6568570</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer i en sänka mellan hällmarker.</t>
+          <t>Över femtio knärot i mossan. Äldre skogsparti i sänka mellan hällmarker. Lokalt fuktig miljö. Näshultaånstrax nedanför bidrar tillett gynnsamt klimat naturvårdsareter som knärot, mfl.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,6 +1245,145 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123102431</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Näshulta kvarn, Näshulta kvarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572672</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568575</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mindre hackspett hördes under några minuter.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
         <v>123102431</v>
       </c>
       <c r="B6" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
         <v>123102431</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
         <v>123102431</v>
       </c>
       <c r="B6" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 2514-2025 artfynd.xlsx
+++ b/artfynd/A 2514-2025 artfynd.xlsx
@@ -1250,7 +1250,7 @@
         <v>123102431</v>
       </c>
       <c r="B6" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
